--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_0_bus.xlsx
@@ -68,19 +68,19 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
-  </si>
-  <si>
-    <t>Bus_2</t>
   </si>
   <si>
     <t>Bus_3</t>
   </si>
   <si>
     <t>Bus_4</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
+  </si>
+  <si>
+    <t>Bus_2</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -526,22 +526,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>5.248639108480242</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1000.000056712887</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.324394473835045</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13.24394453564036</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.248639108480242</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1000.000056712887</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.324394473835046</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13.24394453564036</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -707,66 +707,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.545454803106272</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="D2">
-        <v>4.545454803106272</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>288.6751509578952</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="G2">
-        <v>288.6751509578952</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.9526279647800194</v>
+        <v>0.9526279647803685</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279647840341</v>
+        <v>0.9526279647833883</v>
       </c>
       <c r="Q2">
-        <v>-1.616633113579923E-10</v>
+        <v>-8.694771213770578E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>-179.9999999999736</v>
+        <v>-179.9999999999071</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -805,27 +805,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279646668465</v>
+        <v>0.9526279646671957</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648972067</v>
+        <v>0.9526279648965608</v>
       </c>
       <c r="Q3">
-        <v>7.092595352953472E-11</v>
+        <v>1.457076463161108E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999997791</v>
+        <v>179.9999999998455</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -864,27 +864,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279646400753</v>
+        <v>0.9526279646404244</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279649239781</v>
+        <v>0.952627964923332</v>
       </c>
       <c r="Q4">
-        <v>1.490050607558866E-09</v>
+        <v>1.564819880765525E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.99999999836</v>
+        <v>179.9999999984264</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -923,27 +923,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279644479528</v>
+        <v>0.9526279644483023</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279651161</v>
+        <v>0.9526279651154543</v>
       </c>
       <c r="Q5">
-        <v>2.651384140539186E-09</v>
+        <v>2.726157955097815E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999971986</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279644479528</v>
+        <v>0.9526279644483023</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279651161</v>
+        <v>0.9526279651154542</v>
       </c>
       <c r="Q6">
-        <v>2.651384140539186E-09</v>
+        <v>2.726157955097675E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999971986</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
   </sheetData>
@@ -1071,66 +1071,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.734156921376964</v>
+        <v>3.734156921377197</v>
       </c>
       <c r="D2">
-        <v>3.734156921376964</v>
+        <v>3.734156921377197</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>237.1508154128624</v>
+        <v>237.1508154128772</v>
       </c>
       <c r="G2">
-        <v>237.1508154128624</v>
+        <v>237.1508154128772</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>1.020226441407747</v>
+        <v>1.020226441408047</v>
       </c>
       <c r="O2">
-        <v>0.2400406982755333</v>
+        <v>0.2400406982758468</v>
       </c>
       <c r="P2">
-        <v>0.8960735769158272</v>
+        <v>0.8960735769153692</v>
       </c>
       <c r="Q2">
-        <v>5.766209884958115</v>
+        <v>5.76620988499712</v>
       </c>
       <c r="R2">
-        <v>-121.3466079961244</v>
+        <v>-121.3466079962484</v>
       </c>
       <c r="S2">
-        <v>173.4315681772323</v>
+        <v>173.4315681772755</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1169,27 +1169,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.02022644131472</v>
+        <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981627047</v>
+        <v>0.2400406981630189</v>
       </c>
       <c r="P3">
-        <v>0.896073577006631</v>
+        <v>0.8960735770061724</v>
       </c>
       <c r="Q3">
-        <v>5.76620988493809</v>
+        <v>5.766209884977171</v>
       </c>
       <c r="R3">
-        <v>-121.3466079608125</v>
+        <v>-121.3466079609365</v>
       </c>
       <c r="S3">
-        <v>173.4315681785251</v>
+        <v>173.4315681785683</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1228,27 +1228,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.020226441292007</v>
+        <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981648554</v>
+        <v>0.2400406981651695</v>
       </c>
       <c r="P4">
-        <v>0.8960735770327796</v>
+        <v>0.8960735770323208</v>
       </c>
       <c r="Q4">
-        <v>5.766209885978983</v>
+        <v>5.766209886018058</v>
       </c>
       <c r="R4">
-        <v>-121.346607946827</v>
+        <v>-121.346607946951</v>
       </c>
       <c r="S4">
-        <v>173.4315681776776</v>
+        <v>173.4315681777208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1287,27 +1287,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.020226441140883</v>
+        <v>1.020226441141184</v>
       </c>
       <c r="O5">
-        <v>0.2400406979974898</v>
+        <v>0.2400406979978039</v>
       </c>
       <c r="P5">
-        <v>0.8960735771824243</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q5">
-        <v>5.766209886507372</v>
+        <v>5.766209886546458</v>
       </c>
       <c r="R5">
-        <v>-121.3466078865858</v>
+        <v>-121.3466078867098</v>
       </c>
       <c r="S5">
-        <v>173.4315681791541</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.020226441140883</v>
+        <v>1.020226441141183</v>
       </c>
       <c r="O6">
-        <v>0.2400406979974898</v>
+        <v>0.240040697997804</v>
       </c>
       <c r="P6">
-        <v>0.8960735771824243</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q6">
-        <v>5.766209886507372</v>
+        <v>5.766209886546459</v>
       </c>
       <c r="R6">
-        <v>-121.3466078865858</v>
+        <v>-121.3466078867098</v>
       </c>
       <c r="S6">
-        <v>173.4315681791541</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
   </sheetData>
@@ -1435,66 +1435,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.734156921376964</v>
+        <v>3.734156921377196</v>
       </c>
       <c r="D2">
-        <v>3.734156921376964</v>
+        <v>3.734156921377196</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>237.1508154128624</v>
+        <v>237.1508154128771</v>
       </c>
       <c r="G2">
-        <v>237.1508154128624</v>
+        <v>237.1508154128771</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>1.020226441407747</v>
+        <v>1.020226441408047</v>
       </c>
       <c r="O2">
-        <v>0.2400406982755333</v>
+        <v>0.240040698275847</v>
       </c>
       <c r="P2">
-        <v>0.8960735769158272</v>
+        <v>0.8960735769153693</v>
       </c>
       <c r="Q2">
-        <v>5.766209884958115</v>
+        <v>5.766209884997118</v>
       </c>
       <c r="R2">
-        <v>-121.3466079961244</v>
+        <v>-121.3466079962483</v>
       </c>
       <c r="S2">
-        <v>173.4315681772323</v>
+        <v>173.4315681772755</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1533,27 +1533,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.02022644131472</v>
+        <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981627047</v>
+        <v>0.2400406981630185</v>
       </c>
       <c r="P3">
-        <v>0.896073577006631</v>
+        <v>0.8960735770061726</v>
       </c>
       <c r="Q3">
-        <v>5.76620988493809</v>
+        <v>5.766209884977147</v>
       </c>
       <c r="R3">
-        <v>-121.3466079608125</v>
+        <v>-121.3466079609364</v>
       </c>
       <c r="S3">
-        <v>173.4315681785251</v>
+        <v>173.4315681785683</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1592,27 +1592,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.020226441292007</v>
+        <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981648554</v>
+        <v>0.2400406981651691</v>
       </c>
       <c r="P4">
-        <v>0.8960735770327796</v>
+        <v>0.8960735770323209</v>
       </c>
       <c r="Q4">
-        <v>5.766209885978983</v>
+        <v>5.766209886018035</v>
       </c>
       <c r="R4">
-        <v>-121.346607946827</v>
+        <v>-121.346607946951</v>
       </c>
       <c r="S4">
-        <v>173.4315681776776</v>
+        <v>173.4315681777208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1651,27 +1651,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.020226441133687</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O5">
-        <v>0.24004069798952</v>
+        <v>0.2400406979898336</v>
       </c>
       <c r="P5">
-        <v>0.8960735771895503</v>
+        <v>0.8960735771890918</v>
       </c>
       <c r="Q5">
-        <v>5.766209886532531</v>
+        <v>5.766209886571599</v>
       </c>
       <c r="R5">
-        <v>-121.3466078837171</v>
+        <v>-121.3466078838411</v>
       </c>
       <c r="S5">
-        <v>173.4315681792244</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.020226441133687</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O6">
-        <v>0.24004069798952</v>
+        <v>0.2400406979898336</v>
       </c>
       <c r="P6">
-        <v>0.8960735771895503</v>
+        <v>0.8960735771890916</v>
       </c>
       <c r="Q6">
-        <v>5.766209886532531</v>
+        <v>5.766209886571599</v>
       </c>
       <c r="R6">
-        <v>-121.3466078837171</v>
+        <v>-121.3466078838411</v>
       </c>
       <c r="S6">
-        <v>173.4315681792244</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
   </sheetData>
@@ -1799,66 +1799,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754529</v>
+        <v>3.636363763754283</v>
       </c>
       <c r="D2">
-        <v>3.636363763754529</v>
+        <v>3.636363763754283</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662586</v>
+        <v>230.940115766243</v>
       </c>
       <c r="G2">
-        <v>230.9401157662586</v>
+        <v>230.940115766243</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037849177</v>
+        <v>0.8660254037845061</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037842836</v>
+        <v>0.8660254037849899</v>
       </c>
       <c r="Q2">
-        <v>2.783743888138192E-10</v>
+        <v>1.719777215103925E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.999999999919</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1897,27 +1897,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254036793792</v>
+        <v>0.866025403678968</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.866025403889822</v>
+        <v>0.8660254038905283</v>
       </c>
       <c r="Q3">
-        <v>5.169705539409094E-10</v>
+        <v>4.106762039962387E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999996802</v>
+        <v>179.9999999995807</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1956,27 +1956,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254036550418</v>
+        <v>0.8660254036546307</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254039141595</v>
+        <v>0.8660254039148658</v>
       </c>
       <c r="Q4">
-        <v>3.241688923388843E-09</v>
+        <v>3.1353893656867E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999969555</v>
+        <v>179.9999999968559</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2015,27 +2015,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.866025403479924</v>
+        <v>0.8660254034795128</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.866025404089277</v>
+        <v>0.8660254040899836</v>
       </c>
       <c r="Q5">
-        <v>4.406090147839683E-09</v>
+        <v>4.299807398567792E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999957911</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.866025403479924</v>
+        <v>0.8660254034795128</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.866025404089277</v>
+        <v>0.8660254040899836</v>
       </c>
       <c r="Q6">
-        <v>4.406090147839683E-09</v>
+        <v>4.299803157828283E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999957911</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2163,66 +2163,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754529</v>
+        <v>3.636363763754283</v>
       </c>
       <c r="D2">
-        <v>3.636363763754529</v>
+        <v>3.636363763754283</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662586</v>
+        <v>230.940115766243</v>
       </c>
       <c r="G2">
-        <v>230.9401157662586</v>
+        <v>230.940115766243</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037849177</v>
+        <v>0.8660254037845061</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037842836</v>
+        <v>0.8660254037849899</v>
       </c>
       <c r="Q2">
-        <v>2.783743888138192E-10</v>
+        <v>1.719777215103925E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.999999999919</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2261,27 +2261,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254036793792</v>
+        <v>0.866025403678968</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.866025403889822</v>
+        <v>0.8660254038905283</v>
       </c>
       <c r="Q3">
-        <v>5.169705539409094E-10</v>
+        <v>4.106762039962387E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999996802</v>
+        <v>179.9999999995807</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2320,27 +2320,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254036550418</v>
+        <v>0.8660254036546307</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254039141595</v>
+        <v>0.8660254039148658</v>
       </c>
       <c r="Q4">
-        <v>3.241688923388843E-09</v>
+        <v>3.1353893656867E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999969555</v>
+        <v>179.9999999968559</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2379,27 +2379,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.866025403479924</v>
+        <v>0.8660254034795128</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.866025404089277</v>
+        <v>0.8660254040899836</v>
       </c>
       <c r="Q5">
-        <v>4.406090147839683E-09</v>
+        <v>4.299807398567792E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999957911</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.866025403479924</v>
+        <v>0.8660254034795128</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.866025404089277</v>
+        <v>0.8660254040899836</v>
       </c>
       <c r="Q6">
-        <v>4.406090147839683E-09</v>
+        <v>4.299803157828283E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999957911</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2527,66 +2527,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.055365721222562</v>
+        <v>3.055365721222171</v>
       </c>
       <c r="D2">
-        <v>3.055365721222562</v>
+        <v>3.055365721222171</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>194.0417843782662</v>
+        <v>194.0417843782413</v>
       </c>
       <c r="G2">
-        <v>194.0417843782662</v>
+        <v>194.0417843782413</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.922032494434523</v>
+        <v>0.9220324944339028</v>
       </c>
       <c r="O2">
-        <v>0.1964063473244581</v>
+        <v>0.1964063473242866</v>
       </c>
       <c r="P2">
-        <v>0.8180121061814181</v>
+        <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904171369</v>
+        <v>5.173976904115781</v>
       </c>
       <c r="R2">
-        <v>-122.1449202964103</v>
+        <v>-122.1449202961592</v>
       </c>
       <c r="S2">
-        <v>174.1659345853953</v>
+        <v>174.1659345853095</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2625,27 +2625,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943457958</v>
+        <v>0.9220324943451751</v>
       </c>
       <c r="O3">
-        <v>0.1964063472168435</v>
+        <v>0.1964063472166728</v>
       </c>
       <c r="P3">
-        <v>0.8180121062685103</v>
+        <v>0.8180121062689193</v>
       </c>
       <c r="Q3">
-        <v>5.173976904170181</v>
+        <v>5.173976904114562</v>
       </c>
       <c r="R3">
-        <v>-122.144920255248</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
-        <v>174.1659345865834</v>
+        <v>174.1659345864976</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2684,27 +2684,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9220324943241693</v>
+        <v>0.9220324943235484</v>
       </c>
       <c r="O4">
-        <v>0.1964063472445092</v>
+        <v>0.1964063472443386</v>
       </c>
       <c r="P4">
-        <v>0.8180121062962086</v>
+        <v>0.8180121062966174</v>
       </c>
       <c r="Q4">
-        <v>5.173976906275525</v>
+        <v>5.173976906219907</v>
       </c>
       <c r="R4">
-        <v>-122.1449202332295</v>
+        <v>-122.1449202329783</v>
       </c>
       <c r="S4">
-        <v>174.1659345845433</v>
+        <v>174.1659345844574</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2743,27 +2743,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9220324941766094</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.1964063470810525</v>
+        <v>0.196406347080882</v>
       </c>
       <c r="P5">
-        <v>0.8180121064429093</v>
+        <v>0.8180121064433181</v>
       </c>
       <c r="Q5">
-        <v>5.173976906879523</v>
+        <v>5.173976906823913</v>
       </c>
       <c r="R5">
-        <v>-122.1449201613243</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S5">
-        <v>174.1659345858485</v>
+        <v>174.1659345857626</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9220324941766094</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O6">
-        <v>0.1964063470810525</v>
+        <v>0.196406347080882</v>
       </c>
       <c r="P6">
-        <v>0.8180121064429093</v>
+        <v>0.8180121064433181</v>
       </c>
       <c r="Q6">
-        <v>5.173976906879523</v>
+        <v>5.173976906823913</v>
       </c>
       <c r="R6">
-        <v>-122.1449201613243</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S6">
-        <v>174.1659345858485</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -2891,66 +2891,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.055365721222562</v>
+        <v>3.055365721222171</v>
       </c>
       <c r="D2">
-        <v>3.055365721222562</v>
+        <v>3.055365721222171</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>194.0417843782662</v>
+        <v>194.0417843782413</v>
       </c>
       <c r="G2">
-        <v>194.0417843782662</v>
+        <v>194.0417843782413</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.922032494434523</v>
+        <v>0.9220324944339028</v>
       </c>
       <c r="O2">
-        <v>0.1964063473244581</v>
+        <v>0.1964063473242866</v>
       </c>
       <c r="P2">
-        <v>0.8180121061814181</v>
+        <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904171369</v>
+        <v>5.173976904115781</v>
       </c>
       <c r="R2">
-        <v>-122.1449202964103</v>
+        <v>-122.1449202961592</v>
       </c>
       <c r="S2">
-        <v>174.1659345853953</v>
+        <v>174.1659345853095</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2989,27 +2989,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943457958</v>
+        <v>0.9220324943451751</v>
       </c>
       <c r="O3">
-        <v>0.1964063472168435</v>
+        <v>0.1964063472166728</v>
       </c>
       <c r="P3">
-        <v>0.8180121062685103</v>
+        <v>0.8180121062689193</v>
       </c>
       <c r="Q3">
-        <v>5.173976904170181</v>
+        <v>5.173976904114562</v>
       </c>
       <c r="R3">
-        <v>-122.144920255248</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
-        <v>174.1659345865834</v>
+        <v>174.1659345864976</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3048,27 +3048,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9220324943241693</v>
+        <v>0.9220324943235484</v>
       </c>
       <c r="O4">
-        <v>0.1964063472445092</v>
+        <v>0.1964063472443386</v>
       </c>
       <c r="P4">
-        <v>0.8180121062962086</v>
+        <v>0.8180121062966174</v>
       </c>
       <c r="Q4">
-        <v>5.173976906275525</v>
+        <v>5.173976906219907</v>
       </c>
       <c r="R4">
-        <v>-122.1449202332295</v>
+        <v>-122.1449202329783</v>
       </c>
       <c r="S4">
-        <v>174.1659345845433</v>
+        <v>174.1659345844574</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3107,27 +3107,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9220324941766094</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.1964063470810525</v>
+        <v>0.196406347080882</v>
       </c>
       <c r="P5">
-        <v>0.8180121064429093</v>
+        <v>0.8180121064433181</v>
       </c>
       <c r="Q5">
-        <v>5.173976906879523</v>
+        <v>5.173976906823913</v>
       </c>
       <c r="R5">
-        <v>-122.1449201613243</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S5">
-        <v>174.1659345858485</v>
+        <v>174.1659345857626</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9220324941766094</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O6">
-        <v>0.1964063470810525</v>
+        <v>0.196406347080882</v>
       </c>
       <c r="P6">
-        <v>0.8180121064429093</v>
+        <v>0.8180121064433181</v>
       </c>
       <c r="Q6">
-        <v>5.173976906879523</v>
+        <v>5.173976906823913</v>
       </c>
       <c r="R6">
-        <v>-122.1449201613243</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S6">
-        <v>174.1659345858485</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>5.248639108051611</v>
+        <v>5.248639108526413</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>333.3333522104075</v>
+        <v>333.3333522405614</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3279,48 +3279,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853094052868</v>
+        <v>0.6350853098740156</v>
       </c>
       <c r="O2">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P2">
-        <v>0.6350853104671182</v>
+        <v>0.6350853099409385</v>
       </c>
       <c r="Q2">
-        <v>59.99999996637484</v>
+        <v>59.99999999685334</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999997</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>119.9999999783035</v>
+        <v>119.9999999996535</v>
       </c>
       <c r="T2">
-        <v>5.248639108051611</v>
+        <v>5.248639108526412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3359,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853095206832</v>
+        <v>0.6350853099894118</v>
       </c>
       <c r="O3">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P3">
-        <v>0.6350853103561898</v>
+        <v>0.6350853098300097</v>
       </c>
       <c r="Q3">
-        <v>59.99999997192061</v>
+        <v>60.00000000239913</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999919</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S3">
-        <v>119.9999999845473</v>
+        <v>120.0000000058974</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853095610772</v>
+        <v>0.6350853100298056</v>
       </c>
       <c r="O4">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P4">
-        <v>0.6350853103430411</v>
+        <v>0.635085309816861</v>
       </c>
       <c r="Q4">
-        <v>59.99999997118637</v>
+        <v>60.00000000166487</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999919</v>
+        <v>-89.99999999999585</v>
       </c>
       <c r="S4">
-        <v>119.9999999880705</v>
+        <v>120.0000000094205</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.635085309755108</v>
+        <v>0.6350853102238364</v>
       </c>
       <c r="O5">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.6350853101702927</v>
+        <v>0.6350853096441128</v>
       </c>
       <c r="Q5">
-        <v>59.99999997907577</v>
+        <v>60.00000000955426</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999918</v>
+        <v>-89.99999999999585</v>
       </c>
       <c r="S5">
-        <v>119.9999999992855</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.635085309755108</v>
+        <v>0.6350853102238364</v>
       </c>
       <c r="O6">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.6350853101702927</v>
+        <v>0.6350853096441128</v>
       </c>
       <c r="Q6">
-        <v>59.99999997907577</v>
+        <v>60.00000000955426</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999918</v>
+        <v>-89.99999999999585</v>
       </c>
       <c r="S6">
-        <v>119.9999999992855</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>5.248639108051611</v>
+        <v>5.248639108526413</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>333.3333522104075</v>
+        <v>333.3333522405614</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3661,48 +3661,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853094052868</v>
+        <v>0.6350853098740156</v>
       </c>
       <c r="O2">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P2">
-        <v>0.6350853104671182</v>
+        <v>0.6350853099409385</v>
       </c>
       <c r="Q2">
-        <v>59.99999996637484</v>
+        <v>59.99999999685334</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999997</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>119.9999999783035</v>
+        <v>119.9999999996536</v>
       </c>
       <c r="T2">
-        <v>5.248639108051611</v>
+        <v>5.248639108526412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853095206832</v>
+        <v>0.6350853099894118</v>
       </c>
       <c r="O3">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P3">
-        <v>0.6350853103561898</v>
+        <v>0.6350853098300098</v>
       </c>
       <c r="Q3">
-        <v>59.99999997192061</v>
+        <v>60.00000000239911</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999919</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S3">
-        <v>119.9999999845473</v>
+        <v>120.0000000058974</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3803,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853095610772</v>
+        <v>0.6350853100298056</v>
       </c>
       <c r="O4">
-        <v>1.100000023884006</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P4">
-        <v>0.6350853103430411</v>
+        <v>0.6350853098168611</v>
       </c>
       <c r="Q4">
-        <v>59.99999997118637</v>
+        <v>60.00000000166486</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999919</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S4">
-        <v>119.9999999880705</v>
+        <v>120.0000000094205</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6350853097643474</v>
+        <v>0.635085310233076</v>
       </c>
       <c r="O5">
-        <v>1.100000023884007</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.6350853101620668</v>
+        <v>0.6350853096358871</v>
       </c>
       <c r="Q5">
-        <v>59.99999997945145</v>
+        <v>60.00000000992993</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999918</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S5">
-        <v>119.9999999998196</v>
+        <v>120.0000000211696</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6350853097643474</v>
+        <v>0.635085310233076</v>
       </c>
       <c r="O6">
-        <v>1.100000023884007</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.6350853101620668</v>
+        <v>0.6350853096358871</v>
       </c>
       <c r="Q6">
-        <v>59.99999997945145</v>
+        <v>60.00000000992993</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999918</v>
+        <v>-89.99999999999584</v>
       </c>
       <c r="S6">
-        <v>119.9999999998196</v>
+        <v>120.0000000211696</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960381730407</v>
+        <v>3.617960382473001</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>229.7713440340397</v>
+        <v>229.7713440812008</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4043,48 +4043,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6918398876902114</v>
+        <v>0.6918398877278028</v>
       </c>
       <c r="O2">
-        <v>1.100000023874411</v>
+        <v>1.100000023874158</v>
       </c>
       <c r="P2">
-        <v>0.8378427581691312</v>
+        <v>0.8378427578966809</v>
       </c>
       <c r="Q2">
-        <v>40.4095179335679</v>
+        <v>40.40951795604943</v>
       </c>
       <c r="R2">
-        <v>-90.00000000000263</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S2">
-        <v>128.9574716935018</v>
+        <v>128.9574716956184</v>
       </c>
       <c r="T2">
-        <v>3.617960381730407</v>
+        <v>3.617960382473002</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4123,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6918398877338525</v>
+        <v>0.691839887771443</v>
       </c>
       <c r="O3">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P3">
-        <v>0.8378427580892004</v>
+        <v>0.83784275781675</v>
       </c>
       <c r="Q3">
-        <v>40.4095179400988</v>
+        <v>40.40951796258039</v>
       </c>
       <c r="R3">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999618</v>
       </c>
       <c r="S3">
-        <v>128.9574716963487</v>
+        <v>128.9574716984651</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4185,22 +4185,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877602601</v>
+        <v>0.6918398877978507</v>
       </c>
       <c r="O4">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P4">
-        <v>0.8378427580780752</v>
+        <v>0.8378427578056244</v>
       </c>
       <c r="Q4">
-        <v>40.40951794096504</v>
+        <v>40.40951796344662</v>
       </c>
       <c r="R4">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999618</v>
       </c>
       <c r="S4">
-        <v>128.9574716981358</v>
+        <v>128.9574717002523</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.691839887839602</v>
+        <v>0.6918398878771925</v>
       </c>
       <c r="O5">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.8378427579527064</v>
+        <v>0.8378427576802555</v>
       </c>
       <c r="Q5">
-        <v>40.40951795118443</v>
+        <v>40.40951797366601</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999618</v>
       </c>
       <c r="S5">
-        <v>128.9574717033461</v>
+        <v>128.9574717054625</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.691839887839602</v>
+        <v>0.6918398878771925</v>
       </c>
       <c r="O6">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.8378427579527064</v>
+        <v>0.8378427576802555</v>
       </c>
       <c r="Q6">
-        <v>40.40951795118443</v>
+        <v>40.40951797366601</v>
       </c>
       <c r="R6">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999618</v>
       </c>
       <c r="S6">
-        <v>128.9574717033461</v>
+        <v>128.9574717054625</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108480242</v>
@@ -4374,7 +4374,7 @@
         <v>1000.000056712887</v>
       </c>
       <c r="D2">
-        <v>1.324394473835047</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
@@ -4383,12 +4383,12 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566904</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960381730407</v>
+        <v>3.617960382473001</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4564,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>229.7713440340397</v>
+        <v>229.7713440812008</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4573,48 +4573,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6918398876902114</v>
+        <v>0.6918398877278029</v>
       </c>
       <c r="O2">
-        <v>1.100000023874411</v>
+        <v>1.100000023874158</v>
       </c>
       <c r="P2">
-        <v>0.8378427581691312</v>
+        <v>0.8378427578966809</v>
       </c>
       <c r="Q2">
-        <v>40.4095179335679</v>
+        <v>40.40951795604943</v>
       </c>
       <c r="R2">
-        <v>-90.00000000000263</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S2">
-        <v>128.9574716935018</v>
+        <v>128.9574716956184</v>
       </c>
       <c r="T2">
-        <v>3.617960381730407</v>
+        <v>3.617960382473002</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6918398877338525</v>
+        <v>0.691839887771443</v>
       </c>
       <c r="O3">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P3">
-        <v>0.8378427580892004</v>
+        <v>0.83784275781675</v>
       </c>
       <c r="Q3">
-        <v>40.4095179400988</v>
+        <v>40.40951796258038</v>
       </c>
       <c r="R3">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S3">
-        <v>128.9574716963487</v>
+        <v>128.9574716984652</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4715,22 +4715,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877602601</v>
+        <v>0.6918398877978507</v>
       </c>
       <c r="O4">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P4">
-        <v>0.8378427580780752</v>
+        <v>0.8378427578056247</v>
       </c>
       <c r="Q4">
-        <v>40.40951794096504</v>
+        <v>40.40951796344661</v>
       </c>
       <c r="R4">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S4">
-        <v>128.9574716981358</v>
+        <v>128.9574717002523</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6918398878433802</v>
+        <v>0.6918398878809707</v>
       </c>
       <c r="O5">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.8378427579467363</v>
+        <v>0.8378427576742858</v>
       </c>
       <c r="Q5">
-        <v>40.40951795167106</v>
+        <v>40.40951797415263</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S5">
-        <v>128.9574717035941</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6918398878433802</v>
+        <v>0.6918398878809707</v>
       </c>
       <c r="O6">
-        <v>1.100000023874418</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.8378427579467363</v>
+        <v>0.8378427576742858</v>
       </c>
       <c r="Q6">
-        <v>40.40951795167106</v>
+        <v>40.40951797415263</v>
       </c>
       <c r="R6">
-        <v>-90.00000000000226</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S6">
-        <v>128.9574717035941</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4934,10 +4934,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195465507</v>
+        <v>4.198911195792622</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>266.6666759905878</v>
+        <v>266.6666760113624</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4955,48 +4955,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502687399537</v>
+        <v>0.5773502691155638</v>
       </c>
       <c r="O2">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P2">
-        <v>0.577350269674766</v>
+        <v>0.5773502692541784</v>
       </c>
       <c r="Q2">
-        <v>59.99999996969474</v>
+        <v>59.99999999647622</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999643</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>119.999999976737</v>
+        <v>119.9999999955745</v>
       </c>
       <c r="T2">
-        <v>4.198911195465508</v>
+        <v>4.198911195792622</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502688475657</v>
+        <v>0.5773502692231759</v>
       </c>
       <c r="O3">
-        <v>0.9999999999952228</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P3">
-        <v>0.5773502695713196</v>
+        <v>0.5773502691507325</v>
       </c>
       <c r="Q3">
-        <v>59.99999997538358</v>
+        <v>60.00000000216506</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S3">
-        <v>119.9999999831419</v>
+        <v>120.0000000019794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502688956808</v>
+        <v>0.577350269271291</v>
       </c>
       <c r="O4">
-        <v>0.9999999999952228</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P4">
-        <v>0.5773502695707599</v>
+        <v>0.5773502691501727</v>
       </c>
       <c r="Q4">
-        <v>59.99999997269095</v>
+        <v>59.99999999947241</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>119.9999999886234</v>
+        <v>120.0000000074609</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5773502690809598</v>
+        <v>0.5773502694565701</v>
       </c>
       <c r="O5">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P5">
-        <v>0.5773502694058034</v>
+        <v>0.5773502689852162</v>
       </c>
       <c r="Q5">
-        <v>59.99999998097786</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>120.0000000004035</v>
+        <v>120.000000019241</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5773502690809598</v>
+        <v>0.5773502694565701</v>
       </c>
       <c r="O6">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P6">
-        <v>0.5773502694058034</v>
+        <v>0.5773502689852162</v>
       </c>
       <c r="Q6">
-        <v>59.99999998097786</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>120.0000000004035</v>
+        <v>120.000000019241</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5316,10 +5316,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195465507</v>
+        <v>4.198911195792622</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>266.6666759905878</v>
+        <v>266.6666760113624</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5337,48 +5337,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502687399537</v>
+        <v>0.5773502691155638</v>
       </c>
       <c r="O2">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P2">
-        <v>0.577350269674766</v>
+        <v>0.5773502692541784</v>
       </c>
       <c r="Q2">
-        <v>59.99999996969474</v>
+        <v>59.99999999647622</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999643</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>119.999999976737</v>
+        <v>119.9999999955745</v>
       </c>
       <c r="T2">
-        <v>4.198911195465508</v>
+        <v>4.198911195792622</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502688475657</v>
+        <v>0.5773502692231759</v>
       </c>
       <c r="O3">
-        <v>0.9999999999952228</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P3">
-        <v>0.5773502695713196</v>
+        <v>0.5773502691507325</v>
       </c>
       <c r="Q3">
-        <v>59.99999997538358</v>
+        <v>60.00000000216506</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S3">
-        <v>119.9999999831419</v>
+        <v>120.0000000019794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5479,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502688956808</v>
+        <v>0.577350269271291</v>
       </c>
       <c r="O4">
-        <v>0.9999999999952228</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P4">
-        <v>0.5773502695707599</v>
+        <v>0.5773502691501727</v>
       </c>
       <c r="Q4">
-        <v>59.99999997269095</v>
+        <v>59.99999999947241</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>119.9999999886234</v>
+        <v>120.0000000074609</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5773502690809598</v>
+        <v>0.5773502694565701</v>
       </c>
       <c r="O5">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P5">
-        <v>0.5773502694058034</v>
+        <v>0.5773502689852162</v>
       </c>
       <c r="Q5">
-        <v>59.99999998097786</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>120.0000000004035</v>
+        <v>120.000000019241</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5773502690809598</v>
+        <v>0.5773502694565701</v>
       </c>
       <c r="O6">
-        <v>0.9999999999952227</v>
+        <v>0.9999999999962959</v>
       </c>
       <c r="P6">
-        <v>0.5773502694058034</v>
+        <v>0.5773502689852162</v>
       </c>
       <c r="Q6">
-        <v>59.99999998097786</v>
+        <v>60.00000000775931</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>120.0000000004035</v>
+        <v>120.000000019241</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5698,10 +5698,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>3.012913138226506</v>
+        <v>3.012913138756735</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>191.3456832540037</v>
+        <v>191.3456832876778</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -5719,48 +5719,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.6184267549470447</v>
+        <v>0.6184267549947473</v>
       </c>
       <c r="O2">
-        <v>0.9999999999898747</v>
+        <v>0.9999999999908645</v>
       </c>
       <c r="P2">
-        <v>0.7472997529707802</v>
+        <v>0.747299752735181</v>
       </c>
       <c r="Q2">
-        <v>41.77463360952857</v>
+        <v>41.77463363119257</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999888</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S2">
-        <v>128.1091583172224</v>
+        <v>128.1091583196818</v>
       </c>
       <c r="T2">
-        <v>3.012913138226506</v>
+        <v>3.012913138756735</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5799,22 +5799,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6184267549927183</v>
+        <v>0.6184267550404211</v>
       </c>
       <c r="O3">
-        <v>0.999999999989881</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P3">
-        <v>0.7472997528933965</v>
+        <v>0.7472997526577979</v>
       </c>
       <c r="Q3">
-        <v>41.77463361644245</v>
+        <v>41.7746336381064</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S3">
-        <v>128.1091583203514</v>
+        <v>128.1091583228108</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5861,22 +5861,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6184267550323472</v>
+        <v>0.61842675508005</v>
       </c>
       <c r="O4">
-        <v>0.999999999989881</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P4">
-        <v>0.747299752890124</v>
+        <v>0.7472997526545253</v>
       </c>
       <c r="Q4">
-        <v>41.77463361651106</v>
+        <v>41.77463363817501</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S4">
-        <v>128.1091583233799</v>
+        <v>128.1091583258393</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6184267551165078</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O5">
-        <v>0.9999999999898811</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P5">
-        <v>0.7472997527658994</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q5">
-        <v>41.77463362754426</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>128.1091583292356</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6184267551165078</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O6">
-        <v>0.9999999999898811</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P6">
-        <v>0.7472997527658994</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q6">
-        <v>41.77463362754426</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>128.1091583292356</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6080,10 +6080,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>3.012913138226506</v>
+        <v>3.012913138756735</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>191.3456832540037</v>
+        <v>191.3456832876778</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -6101,48 +6101,48 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.6184267549470447</v>
+        <v>0.6184267549947473</v>
       </c>
       <c r="O2">
-        <v>0.9999999999898747</v>
+        <v>0.9999999999908645</v>
       </c>
       <c r="P2">
-        <v>0.7472997529707802</v>
+        <v>0.747299752735181</v>
       </c>
       <c r="Q2">
-        <v>41.77463360952857</v>
+        <v>41.77463363119257</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999888</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S2">
-        <v>128.1091583172224</v>
+        <v>128.1091583196818</v>
       </c>
       <c r="T2">
-        <v>3.012913138226506</v>
+        <v>3.012913138756735</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6181,22 +6181,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6184267549927183</v>
+        <v>0.6184267550404211</v>
       </c>
       <c r="O3">
-        <v>0.999999999989881</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P3">
-        <v>0.7472997528933965</v>
+        <v>0.7472997526577979</v>
       </c>
       <c r="Q3">
-        <v>41.77463361644245</v>
+        <v>41.7746336381064</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S3">
-        <v>128.1091583203514</v>
+        <v>128.1091583228108</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6243,22 +6243,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6184267550323472</v>
+        <v>0.61842675508005</v>
       </c>
       <c r="O4">
-        <v>0.999999999989881</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P4">
-        <v>0.747299752890124</v>
+        <v>0.7472997526545253</v>
       </c>
       <c r="Q4">
-        <v>41.77463361651106</v>
+        <v>41.77463363817501</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S4">
-        <v>128.1091583233799</v>
+        <v>128.1091583258393</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6184267551165078</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O5">
-        <v>0.9999999999898811</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P5">
-        <v>0.7472997527658994</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q5">
-        <v>41.77463362754426</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>128.1091583292356</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6184267551165078</v>
+        <v>0.6184267551642108</v>
       </c>
       <c r="O6">
-        <v>0.9999999999898811</v>
+        <v>0.9999999999908711</v>
       </c>
       <c r="P6">
-        <v>0.7472997527658994</v>
+        <v>0.7472997525303007</v>
       </c>
       <c r="Q6">
-        <v>41.77463362754426</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999849</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>128.1091583292356</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6462,69 +6462,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5.248639112610032</v>
+        <v>5.248639108736851</v>
       </c>
       <c r="D2">
-        <v>5.248639103623685</v>
+        <v>5.248639107970815</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>333.3333524999061</v>
+        <v>333.3333522539261</v>
       </c>
       <c r="G2">
-        <v>333.3333519291965</v>
+        <v>333.3333522052762</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853098920601</v>
+        <v>0.6350853098347083</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6350853099094727</v>
+        <v>0.6350853098507082</v>
       </c>
       <c r="Q2">
-        <v>-5.687320481010798E-08</v>
+        <v>-4.877429805004033E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999441213</v>
+        <v>179.999999996043</v>
       </c>
       <c r="T2">
-        <v>5.248639107469879</v>
+        <v>5.248639108420277</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.635085309781126</v>
+        <v>0.6350853097237747</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350853100248732</v>
+        <v>0.635085309966109</v>
       </c>
       <c r="Q3">
-        <v>-5.062840951377749E-08</v>
+        <v>1.367246307663144E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.999999949668</v>
+        <v>-179.9999999983958</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6625,22 +6625,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853097679773</v>
+        <v>0.6350853097106262</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6350853100652671</v>
+        <v>0.6350853100065028</v>
       </c>
       <c r="Q4">
-        <v>-4.710528599718108E-08</v>
+        <v>4.890364269927851E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999489338</v>
+        <v>-179.9999999991301</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6350853095952289</v>
+        <v>0.6350853095378781</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6350853102592978</v>
+        <v>0.6350853102005336</v>
       </c>
       <c r="Q5">
-        <v>-3.589025802230296E-08</v>
+        <v>1.610542098861925E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999568232</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6350853095952289</v>
+        <v>0.6350853095378781</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6350853102592978</v>
+        <v>0.6350853102005336</v>
       </c>
       <c r="Q6">
-        <v>-3.589025802230296E-08</v>
+        <v>1.610542099157694E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999568232</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6844,69 +6844,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5.248639112610032</v>
+        <v>5.24863910873685</v>
       </c>
       <c r="D2">
-        <v>5.248639103623685</v>
+        <v>5.248639107970815</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>333.3333524999061</v>
+        <v>333.333352253926</v>
       </c>
       <c r="G2">
-        <v>333.3333519291965</v>
+        <v>333.3333522052762</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6350853098920601</v>
+        <v>0.6350853098347087</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6350853099094727</v>
+        <v>0.6350853098507082</v>
       </c>
       <c r="Q2">
-        <v>-5.687320481010798E-08</v>
+        <v>-4.877425024049089E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999441213</v>
+        <v>179.999999996043</v>
       </c>
       <c r="T2">
-        <v>5.248639107469879</v>
+        <v>5.248639108420278</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6945,22 +6945,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.635085309781126</v>
+        <v>0.6350853097237747</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350853100248732</v>
+        <v>0.635085309966109</v>
       </c>
       <c r="Q3">
-        <v>-5.062840951377749E-08</v>
+        <v>1.367189660607264E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.999999949668</v>
+        <v>-179.9999999983959</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853097679773</v>
+        <v>0.635085309710626</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6350853100652671</v>
+        <v>0.6350853100065029</v>
       </c>
       <c r="Q4">
-        <v>-4.710528599718108E-08</v>
+        <v>4.89030515153221E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999489338</v>
+        <v>-179.9999999991301</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6350853095870027</v>
+        <v>0.6350853095296518</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6350853102685372</v>
+        <v>0.6350853102097733</v>
       </c>
       <c r="Q5">
-        <v>-3.535620883065298E-08</v>
+        <v>1.663940450147506E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999571988</v>
+        <v>-179.999999990865</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6350853095870027</v>
+        <v>0.6350853095296518</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6350853102685372</v>
+        <v>0.6350853102097733</v>
       </c>
       <c r="Q6">
-        <v>-3.535620883065298E-08</v>
+        <v>1.663940450457329E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999571988</v>
+        <v>-179.999999990865</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7226,69 +7226,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.617960384076857</v>
+        <v>3.617960382593723</v>
       </c>
       <c r="D2">
-        <v>3.617960380005671</v>
+        <v>3.617960382231206</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>229.7713441830593</v>
+        <v>229.7713440888676</v>
       </c>
       <c r="G2">
-        <v>229.7713439245042</v>
+        <v>229.7713440658447</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.8378427579344082</v>
+        <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111894484</v>
+        <v>0.4028253111898904</v>
       </c>
       <c r="P2">
-        <v>0.6918398879186659</v>
+        <v>0.6918398877011798</v>
       </c>
       <c r="Q2">
-        <v>8.957471676237471</v>
+        <v>8.95747169350477</v>
       </c>
       <c r="R2">
-        <v>-115.8807585962768</v>
+        <v>-115.8807585964592</v>
       </c>
       <c r="S2">
-        <v>160.4095179429141</v>
+        <v>160.4095179569557</v>
       </c>
       <c r="T2">
-        <v>3.617960380884718</v>
+        <v>3.617960382370077</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427578544626</v>
+        <v>0.8378427577457516</v>
       </c>
       <c r="O3">
-        <v>0.4028253110947728</v>
+        <v>0.4028253110952158</v>
       </c>
       <c r="P3">
-        <v>0.6918398879622948</v>
+        <v>0.6918398877448089</v>
       </c>
       <c r="Q3">
-        <v>8.957471679084245</v>
+        <v>8.957471696351645</v>
       </c>
       <c r="R3">
-        <v>-115.8807585786222</v>
+        <v>-115.8807585788046</v>
       </c>
       <c r="S3">
-        <v>160.4095179494457</v>
+        <v>160.4095179634873</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7389,22 +7389,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8378427578433371</v>
+        <v>0.8378427577346262</v>
       </c>
       <c r="O4">
-        <v>0.4028253110965774</v>
+        <v>0.4028253110970203</v>
       </c>
       <c r="P4">
-        <v>0.6918398879887024</v>
+        <v>0.6918398877712163</v>
       </c>
       <c r="Q4">
-        <v>8.957471680871423</v>
+        <v>8.957471698138821</v>
       </c>
       <c r="R4">
-        <v>-115.8807585716295</v>
+        <v>-115.8807585718119</v>
       </c>
       <c r="S4">
-        <v>160.4095179503119</v>
+        <v>160.4095179643535</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8378427577179681</v>
+        <v>0.8378427576092574</v>
       </c>
       <c r="O5">
-        <v>0.4028253109561448</v>
+        <v>0.4028253109565879</v>
       </c>
       <c r="P5">
-        <v>0.6918398880680442</v>
+        <v>0.6918398878505582</v>
       </c>
       <c r="Q5">
-        <v>8.957471686081623</v>
+        <v>8.957471703349039</v>
       </c>
       <c r="R5">
-        <v>-115.8807585415089</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S5">
-        <v>160.4095179605313</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8378427577179681</v>
+        <v>0.8378427576092574</v>
       </c>
       <c r="O6">
-        <v>0.4028253109561448</v>
+        <v>0.4028253109565879</v>
       </c>
       <c r="P6">
-        <v>0.6918398880680442</v>
+        <v>0.6918398878505582</v>
       </c>
       <c r="Q6">
-        <v>8.957471686081623</v>
+        <v>8.957471703349039</v>
       </c>
       <c r="R6">
-        <v>-115.8807585415089</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S6">
-        <v>160.4095179605313</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7608,69 +7608,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.617960384076857</v>
+        <v>3.617960382593723</v>
       </c>
       <c r="D2">
-        <v>3.617960380005671</v>
+        <v>3.617960382231207</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>229.7713441830593</v>
+        <v>229.7713440888676</v>
       </c>
       <c r="G2">
-        <v>229.7713439245042</v>
+        <v>229.7713440658447</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.32439447363298</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.8378427579344082</v>
+        <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111894484</v>
+        <v>0.4028253111898906</v>
       </c>
       <c r="P2">
-        <v>0.6918398879186659</v>
+        <v>0.6918398877011797</v>
       </c>
       <c r="Q2">
-        <v>8.957471676237471</v>
+        <v>8.957471693504779</v>
       </c>
       <c r="R2">
-        <v>-115.8807585962768</v>
+        <v>-115.8807585964592</v>
       </c>
       <c r="S2">
-        <v>160.4095179429141</v>
+        <v>160.4095179569557</v>
       </c>
       <c r="T2">
-        <v>3.617960380884718</v>
+        <v>3.617960382370079</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7709,22 +7709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427578544626</v>
+        <v>0.8378427577457515</v>
       </c>
       <c r="O3">
-        <v>0.4028253110947728</v>
+        <v>0.4028253110952154</v>
       </c>
       <c r="P3">
-        <v>0.6918398879622948</v>
+        <v>0.6918398877448089</v>
       </c>
       <c r="Q3">
-        <v>8.957471679084245</v>
+        <v>8.957471696351631</v>
       </c>
       <c r="R3">
-        <v>-115.8807585786222</v>
+        <v>-115.8807585788046</v>
       </c>
       <c r="S3">
-        <v>160.4095179494457</v>
+        <v>160.4095179634873</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8378427578433371</v>
+        <v>0.8378427577346261</v>
       </c>
       <c r="O4">
-        <v>0.4028253110965774</v>
+        <v>0.40282531109702</v>
       </c>
       <c r="P4">
-        <v>0.6918398879887024</v>
+        <v>0.6918398877712163</v>
       </c>
       <c r="Q4">
-        <v>8.957471680871423</v>
+        <v>8.957471698138807</v>
       </c>
       <c r="R4">
-        <v>-115.8807585716295</v>
+        <v>-115.8807585718119</v>
       </c>
       <c r="S4">
-        <v>160.4095179503119</v>
+        <v>160.4095179643535</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8378427577119982</v>
+        <v>0.8378427576032873</v>
       </c>
       <c r="O5">
-        <v>0.4028253109494574</v>
+        <v>0.4028253109499</v>
       </c>
       <c r="P5">
-        <v>0.6918398880718224</v>
+        <v>0.6918398878543364</v>
       </c>
       <c r="Q5">
-        <v>8.957471686329733</v>
+        <v>8.957471703597118</v>
       </c>
       <c r="R5">
-        <v>-115.8807585400746</v>
+        <v>-115.8807585402569</v>
       </c>
       <c r="S5">
-        <v>160.4095179610179</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8378427577119982</v>
+        <v>0.8378427576032873</v>
       </c>
       <c r="O6">
-        <v>0.4028253109494574</v>
+        <v>0.4028253109499</v>
       </c>
       <c r="P6">
-        <v>0.6918398880718224</v>
+        <v>0.6918398878543364</v>
       </c>
       <c r="Q6">
-        <v>8.957471686329733</v>
+        <v>8.957471703597118</v>
       </c>
       <c r="R6">
-        <v>-115.8807585400746</v>
+        <v>-115.8807585402569</v>
       </c>
       <c r="S6">
-        <v>160.4095179610179</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7990,69 +7990,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911198838688</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
-        <v>4.198911192347739</v>
+        <v>4.198911195412808</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666762048136</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
-        <v>266.666675792583</v>
+        <v>266.666675987241</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502692415431</v>
+        <v>0.5773502691952341</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5773502692197645</v>
+        <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.128470651296841E-08</v>
+        <v>-5.812892660336569E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999481273</v>
+        <v>179.9999999936331</v>
       </c>
       <c r="T2">
-        <v>4.198911195154263</v>
+        <v>4.19891119582141</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502691380924</v>
+        <v>0.5773502690917837</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502693273818</v>
+        <v>0.5773502692819933</v>
       </c>
       <c r="Q3">
-        <v>-4.487887049415693E-08</v>
+        <v>5.928493903080363E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999538172</v>
+        <v>179.9999999993227</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8153,22 +8153,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502691375325</v>
+        <v>0.5773502690912239</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693754967</v>
+        <v>0.5773502693301084</v>
       </c>
       <c r="Q4">
-        <v>-3.939737325175305E-08</v>
+        <v>6.074361262583481E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999511245</v>
+        <v>179.9999999966301</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.577350268972576</v>
+        <v>0.5773502689262675</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5773502695607758</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q5">
-        <v>-2.761725263886753E-08</v>
+        <v>1.785448827777802E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999594114</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.577350268972576</v>
+        <v>0.5773502689262675</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5773502695607758</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q6">
-        <v>-2.761725263886753E-08</v>
+        <v>1.785448228161969E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999594114</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498488</v>
@@ -8342,7 +8342,7 @@
         <v>689.314032248458</v>
       </c>
       <c r="D2">
-        <v>1.324394473835045</v>
+        <v>1.324394473835046</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
@@ -8351,12 +8351,12 @@
         <v>0.4028253111823096</v>
       </c>
       <c r="G2">
-        <v>45.00000000004627</v>
+        <v>45.00000000004628</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8371,15 +8371,15 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876384</v>
+        <v>0.4028253110876379</v>
       </c>
       <c r="G3">
-        <v>-25.8807585799728</v>
+        <v>-25.88075857997278</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8394,15 +8394,15 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.402825311089443</v>
+        <v>0.4028253110894425</v>
       </c>
       <c r="G4">
-        <v>-25.88075857298006</v>
+        <v>-25.88075857298004</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8417,15 +8417,15 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.4028253109490105</v>
+        <v>0.4028253109490099</v>
       </c>
       <c r="G5">
-        <v>-25.88075854285943</v>
+        <v>-25.8807585428594</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.4028253109490105</v>
+        <v>0.4028253109490099</v>
       </c>
       <c r="G6">
-        <v>-25.88075854285943</v>
+        <v>-25.8807585428594</v>
       </c>
     </row>
   </sheetData>
@@ -8520,69 +8520,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911198838688</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
-        <v>4.198911192347739</v>
+        <v>4.198911195412808</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666762048136</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
-        <v>266.666675792583</v>
+        <v>266.666675987241</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502692415431</v>
+        <v>0.5773502691952341</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5773502692197645</v>
+        <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.128470651296841E-08</v>
+        <v>-5.812892660336569E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999481273</v>
+        <v>179.9999999936331</v>
       </c>
       <c r="T2">
-        <v>4.198911195154263</v>
+        <v>4.19891119582141</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502691380924</v>
+        <v>0.5773502690917837</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502693273818</v>
+        <v>0.5773502692819933</v>
       </c>
       <c r="Q3">
-        <v>-4.487887049415693E-08</v>
+        <v>5.928493903080363E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999538172</v>
+        <v>179.9999999993227</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8683,22 +8683,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502691375325</v>
+        <v>0.5773502690912239</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693754967</v>
+        <v>0.5773502693301084</v>
       </c>
       <c r="Q4">
-        <v>-3.939737325175305E-08</v>
+        <v>6.074361262583481E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999511245</v>
+        <v>179.9999999966301</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.577350268972576</v>
+        <v>0.5773502689262675</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.5773502695607758</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q5">
-        <v>-2.761725263886753E-08</v>
+        <v>1.785448827777802E-08</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999594114</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.577350268972576</v>
+        <v>0.5773502689262675</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5773502695607758</v>
+        <v>0.5773502695153875</v>
       </c>
       <c r="Q6">
-        <v>-2.761725263886753E-08</v>
+        <v>1.785448228161969E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999594114</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8902,69 +8902,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.012913140111029</v>
+        <v>3.012913138951925</v>
       </c>
       <c r="D2">
-        <v>3.012913136900726</v>
+        <v>3.012913138593919</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>191.3456833736869</v>
+        <v>191.345683300074</v>
       </c>
       <c r="G2">
-        <v>191.3456831698054</v>
+        <v>191.3456832773375</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.7472997528097253</v>
+        <v>0.7472997527192564</v>
       </c>
       <c r="O2">
-        <v>0.3354590831696538</v>
+        <v>0.3354590831689601</v>
       </c>
       <c r="P2">
-        <v>0.6184267552152765</v>
+        <v>0.6184267550384416</v>
       </c>
       <c r="Q2">
-        <v>8.109158302019251</v>
+        <v>8.109158318802283</v>
       </c>
       <c r="R2">
-        <v>-117.0248837770113</v>
+        <v>-117.0248837767962</v>
       </c>
       <c r="S2">
-        <v>161.7746336173196</v>
+        <v>161.7746336318227</v>
       </c>
       <c r="T2">
-        <v>3.012913137670219</v>
+        <v>3.012913138737345</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9003,22 +9003,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7472997527323298</v>
+        <v>0.7472997526418615</v>
       </c>
       <c r="O3">
-        <v>0.3354590830777505</v>
+        <v>0.3354590830770564</v>
       </c>
       <c r="P3">
-        <v>0.6184267552609409</v>
+        <v>0.6184267550841063</v>
       </c>
       <c r="Q3">
-        <v>8.109158305148284</v>
+        <v>8.109158321931375</v>
       </c>
       <c r="R3">
-        <v>-117.0248837564316</v>
+        <v>-117.0248837562165</v>
       </c>
       <c r="S3">
-        <v>161.774633624234</v>
+        <v>161.7746336387373</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9065,22 +9065,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7472997527290575</v>
+        <v>0.7472997526385891</v>
       </c>
       <c r="O4">
-        <v>0.3354590831013768</v>
+        <v>0.3354590831006827</v>
       </c>
       <c r="P4">
-        <v>0.61842675530057</v>
+        <v>0.6184267551237352</v>
       </c>
       <c r="Q4">
-        <v>8.109158308176802</v>
+        <v>8.109158324959898</v>
       </c>
       <c r="R4">
-        <v>-117.0248837454224</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
-        <v>161.7746336243027</v>
+        <v>161.7746336388059</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7472997526048327</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O5">
-        <v>0.3354590829617861</v>
+        <v>0.3354590829610919</v>
       </c>
       <c r="P5">
-        <v>0.6184267553847305</v>
+        <v>0.6184267552078958</v>
       </c>
       <c r="Q5">
-        <v>8.109158314032515</v>
+        <v>8.109158330815621</v>
       </c>
       <c r="R5">
-        <v>-117.0248837094698</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>161.7746336353358</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7472997526048327</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O6">
-        <v>0.3354590829617861</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P6">
-        <v>0.6184267553847305</v>
+        <v>0.6184267552078957</v>
       </c>
       <c r="Q6">
-        <v>8.109158314032515</v>
+        <v>8.109158330815614</v>
       </c>
       <c r="R6">
-        <v>-117.0248837094698</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>161.7746336353358</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9284,69 +9284,69 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.012913140111029</v>
+        <v>3.012913138951925</v>
       </c>
       <c r="D2">
-        <v>3.012913136900726</v>
+        <v>3.012913138593919</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>191.3456833736869</v>
+        <v>191.345683300074</v>
       </c>
       <c r="G2">
-        <v>191.3456831698054</v>
+        <v>191.3456832773375</v>
       </c>
       <c r="H2">
-        <v>1.504993761276267</v>
+        <v>1.504993724976268</v>
       </c>
       <c r="I2">
-        <v>15.04993697142864</v>
+        <v>15.04993697142863</v>
       </c>
       <c r="J2">
         <v>1.504993721671082</v>
       </c>
       <c r="K2">
-        <v>15.04993697236767</v>
+        <v>15.04993697236766</v>
       </c>
       <c r="L2">
-        <v>1.504993720685201</v>
+        <v>1.504993720695517</v>
       </c>
       <c r="M2">
-        <v>15.04993697226168</v>
+        <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.7472997528097253</v>
+        <v>0.7472997527192564</v>
       </c>
       <c r="O2">
-        <v>0.3354590831696538</v>
+        <v>0.3354590831689601</v>
       </c>
       <c r="P2">
-        <v>0.6184267552152765</v>
+        <v>0.6184267550384416</v>
       </c>
       <c r="Q2">
-        <v>8.109158302019251</v>
+        <v>8.109158318802283</v>
       </c>
       <c r="R2">
-        <v>-117.0248837770113</v>
+        <v>-117.0248837767962</v>
       </c>
       <c r="S2">
-        <v>161.7746336173196</v>
+        <v>161.7746336318227</v>
       </c>
       <c r="T2">
-        <v>3.012913137670219</v>
+        <v>3.012913138737345</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9385,22 +9385,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7472997527323298</v>
+        <v>0.7472997526418615</v>
       </c>
       <c r="O3">
-        <v>0.3354590830777505</v>
+        <v>0.3354590830770564</v>
       </c>
       <c r="P3">
-        <v>0.6184267552609409</v>
+        <v>0.6184267550841063</v>
       </c>
       <c r="Q3">
-        <v>8.109158305148284</v>
+        <v>8.109158321931375</v>
       </c>
       <c r="R3">
-        <v>-117.0248837564316</v>
+        <v>-117.0248837562165</v>
       </c>
       <c r="S3">
-        <v>161.774633624234</v>
+        <v>161.7746336387373</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9447,22 +9447,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7472997527290575</v>
+        <v>0.7472997526385891</v>
       </c>
       <c r="O4">
-        <v>0.3354590831013768</v>
+        <v>0.3354590831006827</v>
       </c>
       <c r="P4">
-        <v>0.61842675530057</v>
+        <v>0.6184267551237352</v>
       </c>
       <c r="Q4">
-        <v>8.109158308176802</v>
+        <v>8.109158324959898</v>
       </c>
       <c r="R4">
-        <v>-117.0248837454224</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
-        <v>161.7746336243027</v>
+        <v>161.7746336388059</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7472997526048327</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O5">
-        <v>0.3354590829617861</v>
+        <v>0.3354590829610919</v>
       </c>
       <c r="P5">
-        <v>0.6184267553847305</v>
+        <v>0.6184267552078958</v>
       </c>
       <c r="Q5">
-        <v>8.109158314032515</v>
+        <v>8.109158330815621</v>
       </c>
       <c r="R5">
-        <v>-117.0248837094698</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>161.7746336353358</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7472997526048327</v>
+        <v>0.7472997525143641</v>
       </c>
       <c r="O6">
-        <v>0.3354590829617861</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P6">
-        <v>0.6184267553847305</v>
+        <v>0.6184267552078957</v>
       </c>
       <c r="Q6">
-        <v>8.109158314032515</v>
+        <v>8.109158330815614</v>
       </c>
       <c r="R6">
-        <v>-117.0248837094698</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>161.7746336353358</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9627,30 +9627,30 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960382498489</v>
+        <v>3.617960382498488</v>
       </c>
       <c r="C2">
-        <v>689.3140322484581</v>
+        <v>689.314032248458</v>
       </c>
       <c r="D2">
-        <v>1.324394473835047</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
       </c>
       <c r="F2">
-        <v>0.4028253111823098</v>
+        <v>0.4028253111823097</v>
       </c>
       <c r="G2">
-        <v>45.00000000004626</v>
+        <v>45.00000000004628</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9665,15 +9665,15 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876387</v>
+        <v>0.4028253110876389</v>
       </c>
       <c r="G3">
-        <v>-25.88075857997276</v>
+        <v>-25.88075857997272</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9688,15 +9688,15 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.4028253110894434</v>
+        <v>0.4028253110894437</v>
       </c>
       <c r="G4">
-        <v>-25.88075857298002</v>
+        <v>-25.88075857297997</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9711,15 +9711,15 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.4028253109423234</v>
+        <v>0.4028253109423238</v>
       </c>
       <c r="G5">
-        <v>-25.88075854142508</v>
+        <v>-25.88075854142505</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.4028253109423234</v>
+        <v>0.4028253109423239</v>
       </c>
       <c r="G6">
-        <v>-25.88075854142508</v>
+        <v>-25.88075854142503</v>
       </c>
     </row>
   </sheetData>
@@ -9775,13 +9775,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195753389</v>
+        <v>4.198911195753388</v>
       </c>
       <c r="C2">
-        <v>800.0000280266123</v>
+        <v>800.0000280266122</v>
       </c>
       <c r="D2">
         <v>1.504993721305343</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9923,13 +9923,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195753389</v>
+        <v>4.198911195753388</v>
       </c>
       <c r="C2">
-        <v>800.0000280266123</v>
+        <v>800.0000280266122</v>
       </c>
       <c r="D2">
         <v>1.504993721305343</v>
@@ -9946,7 +9946,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10015,7 +10015,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10089,12 +10089,12 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355207</v>
+        <v>44.99999999355205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10109,15 +10109,15 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3354590830466711</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="G3">
-        <v>-27.02488376071815</v>
+        <v>-27.02488376071819</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10135,12 +10135,12 @@
         <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970884</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10155,15 +10155,15 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307066</v>
+        <v>0.3354590829307067</v>
       </c>
       <c r="G5">
-        <v>-27.02488371375628</v>
+        <v>-27.02488371375633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307066</v>
+        <v>0.3354590829307068</v>
       </c>
       <c r="G6">
-        <v>-27.02488371375628</v>
+        <v>-27.02488371375632</v>
       </c>
     </row>
   </sheetData>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10237,12 +10237,12 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355207</v>
+        <v>44.99999999355205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10257,15 +10257,15 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3354590830466711</v>
+        <v>0.3354590830466712</v>
       </c>
       <c r="G3">
-        <v>-27.02488376071815</v>
+        <v>-27.02488376071819</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10283,12 +10283,12 @@
         <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970884</v>
+        <v>-27.0248837497089</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10303,15 +10303,15 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307066</v>
+        <v>0.3354590829307067</v>
       </c>
       <c r="G5">
-        <v>-27.02488371375628</v>
+        <v>-27.02488371375633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307066</v>
+        <v>0.3354590829307068</v>
       </c>
       <c r="G6">
-        <v>-27.02488371375628</v>
+        <v>-27.02488371375632</v>
       </c>
     </row>
   </sheetData>
@@ -10403,66 +10403,66 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.545454803106272</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="D2">
-        <v>4.545454803106272</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>288.6751509578952</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="G2">
-        <v>288.6751509578952</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="H2">
-        <v>1.324394513719423</v>
+        <v>1.324394477419423</v>
       </c>
       <c r="I2">
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632987</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
       </c>
       <c r="L2">
-        <v>1.324394474108814</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
-        <v>13.24394453564252</v>
+        <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.9526279647800194</v>
+        <v>0.9526279647803685</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279647840341</v>
+        <v>0.9526279647833884</v>
       </c>
       <c r="Q2">
-        <v>-1.616633113579923E-10</v>
+        <v>-8.694480440990813E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>-179.9999999999736</v>
+        <v>-179.9999999999071</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10501,27 +10501,27 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279646668465</v>
+        <v>0.952627964667196</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648972067</v>
+        <v>0.9526279648965608</v>
       </c>
       <c r="Q3">
-        <v>7.092595352953472E-11</v>
+        <v>1.457377749126735E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999997791</v>
+        <v>179.9999999998456</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10560,27 +10560,27 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279646400753</v>
+        <v>0.9526279646404248</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279649239781</v>
+        <v>0.952627964923332</v>
       </c>
       <c r="Q4">
-        <v>1.490050607558866E-09</v>
+        <v>1.56486428040874E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.99999999836</v>
+        <v>179.9999999984264</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10619,27 +10619,27 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279644566856</v>
+        <v>0.9526279644570353</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279651073672</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q5">
-        <v>2.598594644344476E-09</v>
+        <v>2.673424424198795E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999972514</v>
+        <v>179.9999999973179</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279644566856</v>
+        <v>0.9526279644570353</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279651073672</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q6">
-        <v>2.598594644344477E-09</v>
+        <v>2.673424424198816E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999972514</v>
+        <v>179.9999999973179</v>
       </c>
     </row>
   </sheetData>
